--- a/ig/DM-SIDOBA/CodeSystem-TRE-R327-TypeDecision.xlsx
+++ b/ig/DM-SIDOBA/CodeSystem-TRE-R327-TypeDecision.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>8</t>
+    <t>7</t>
   </si>
   <si>
     <t>Code</t>
@@ -236,15 +236,6 @@
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>Nouveau droit</t>
-  </si>
-  <si>
-    <t>Indique si le droit attribué par la CDAPH est un nouveau droit.</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>Renouvellement</t>
@@ -666,7 +657,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -772,27 +763,13 @@
         <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="D8" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
